--- a/output/DP_Member_360/Data_Dictionary_Member_360.xlsx
+++ b/output/DP_Member_360/Data_Dictionary_Member_360.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S2T_Mapping" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Source_Dictionary'!$A$1:$H$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Source_Dictionary'!$A$1:$H$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Target_DP_Member_360'!$A$1:$G$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'S2T_Mapping'!$A$1:$D$11</definedName>
   </definedNames>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2839,8 +2839,206 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>account_id_map (reference)</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>core_banking</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>System the ID comes from (core_banking, fraud_case_mgmt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>account_id_map (reference)</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>source_account_id</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(12)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>A00001</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Account ID as that system writes it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>account_id_map (reference)</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>account_id</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>A0000001</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Canonical ^A\d{7}$ (zero-padded).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>account_id_map (reference)</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>in_core_banking</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Canonical ID exists in core banking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>account_id_map (reference)</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>mapping_rule</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR(40)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>pad_to_7_digits</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Rule used to derive account_id.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H61"/>
+  <autoFilter ref="A1:H66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/DP_Member_360/Data_Dictionary_Member_360.xlsx
+++ b/output/DP_Member_360/Data_Dictionary_Member_360.xlsx
@@ -1030,7 +1030,7 @@
       <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28202</t>
+          <t>28210</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Avery</t>
+          <t>(PII – not shown)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Brooks</t>
+          <t>(PII – not shown)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>28202</t>
+          <t>(PII – not shown)</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
